--- a/sheets/민요/검수/창부타령 (채보1) 창부 타령-3.xlsx
+++ b/sheets/민요/검수/창부타령 (채보1) 창부 타령-3.xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -593,12 +593,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|仲</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -835,12 +835,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -993,12 +993,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|仲</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -1893,12 +1893,12 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|姑</t>
+          <t xml:space="preserve">–|姑</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -2488,13 +2488,13 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―|姑</t>
+          <t xml:space="preserve">姑|–|姑</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―
+–
 姑</t>
         </is>
       </c>
@@ -2568,12 +2568,12 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無|姑</t>
+          <t xml:space="preserve">–|無|姑</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無
 姑</t>
         </is>
@@ -2729,12 +2729,12 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -3019,12 +3019,12 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I64" s="2"/>
@@ -3110,7 +3110,7 @@
       <c r="B3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―
+–
 姑</t>
         </is>
       </c>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="F4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="H4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -3203,7 +3203,7 @@
       <c r="A5" s="0"/>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無
 姑</t>
         </is>
@@ -3379,14 +3379,14 @@
       <c r="A9" s="0"/>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -3438,7 +3438,7 @@
       <c r="G10" s="13"/>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -3578,7 +3578,7 @@
       <c r="E14" s="10"/>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -3688,7 +3688,7 @@
       <c r="A17" s="0"/>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C17" s="9"/>
@@ -3735,7 +3735,7 @@
       <c r="C18" s="10"/>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>

--- a/sheets/민요/검수/창부타령 (채보1) 창부 타령-3.xlsx
+++ b/sheets/민요/검수/창부타령 (채보1) 창부 타령-3.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3092,62 +3133,62 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">창부타령</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –
 姑</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">디리리</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">애</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">너</t>
         </is>
       </c>
-      <c r="H3" s="18" t="inlineStr">
+      <c r="H3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">핀</t>
         </is>
@@ -3155,45 +3196,45 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리리</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">득</t>
         </is>
@@ -3201,45 +3242,45 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無
 姑</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리리</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">도오</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="I5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">슥</t>
         </is>
@@ -3247,44 +3288,44 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">길리이</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">진</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無
 潢</t>
         </is>
       </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="G6" s="26"/>
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無
 潢</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -3292,47 +3333,47 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑
 仲</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">디리</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑
 仲</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">못</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
@@ -3340,36 +3381,36 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="C8" s="27"/>
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="E8" s="27"/>
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙
 仲</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">파</t>
         </is>
       </c>
-      <c r="H8" s="18" t="inlineStr">
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙
 仲</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="I8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -3377,72 +3418,72 @@
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="C9" s="25"/>
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="H9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="I9" s="12"/>
+      <c r="I9" s="27"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="C10" s="28"/>
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="G10" s="13"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="G10" s="28"/>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">슬</t>
         </is>
@@ -3450,42 +3491,42 @@
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="C11" s="22"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">못</t>
         </is>
       </c>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="H11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙
 潢</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="I11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">플</t>
         </is>
@@ -3493,36 +3534,36 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="25"/>
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="E12" s="25"/>
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙
 潢</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="G12" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">살</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="I12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
@@ -3530,70 +3571,70 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="25"/>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="25"/>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">겟</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I13" s="9"/>
+      <c r="I13" s="25"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢
 潢</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="26"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="26"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">쇠</t>
         </is>
@@ -3601,39 +3642,39 @@
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="C15" s="22"/>
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">열</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">숙</t>
         </is>
@@ -3641,44 +3682,44 @@
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="C16" s="25"/>
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 僙
 仲</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">니나</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無
 潢</t>
         </is>
       </c>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="G16" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">씨구나</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無
 潢</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="I16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">명</t>
         </is>
@@ -3686,38 +3727,38 @@
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="C17" s="25"/>
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">노쇠</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">좋구나</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="I17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">적</t>
         </is>
@@ -3725,26 +3766,26 @@
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無
 仲</t>
         </is>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="C18" s="26"/>
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">못하리</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無
@@ -3752,12 +3793,12 @@
 僙</t>
         </is>
       </c>
-      <c r="G18" s="13" t="inlineStr">
+      <c r="G18" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">지화자</t>
         </is>
       </c>
-      <c r="H18" s="18" t="inlineStr">
+      <c r="H18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無
@@ -3765,7 +3806,7 @@
 僙</t>
         </is>
       </c>
-      <c r="I18" s="13" t="inlineStr">
+      <c r="I18" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">인</t>
         </is>

--- a/sheets/민요/검수/창부타령 (채보1) 창부 타령-3.xlsx
+++ b/sheets/민요/검수/창부타령 (채보1) 창부 타령-3.xlsx
@@ -3118,20 +3118,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="108.96" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="108.96" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="108.96" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="108.96" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="108.96" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="108.96" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="108.96" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="23" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="108.96" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="I9" s="27"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="108.96" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="108.96" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="108.96" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="108.96" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="I13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="108.96" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="108.96" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="108.96" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="108.96" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="108.96" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>

--- a/sheets/민요/검수/창부타령 (채보1) 창부 타령-3.xlsx
+++ b/sheets/민요/검수/창부타령 (채보1) 창부 타령-3.xlsx
@@ -3157,7 +3157,9 @@
       </c>
       <c r="C3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">디리리</t>
+          <t xml:space="preserve">디
+리
+리</t>
         </is>
       </c>
       <c r="D3" s="21" t="inlineStr">
@@ -3203,7 +3205,8 @@
       </c>
       <c r="C4" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">리리</t>
+          <t xml:space="preserve">리
+리</t>
         </is>
       </c>
       <c r="D4" s="21" t="inlineStr">
@@ -3251,7 +3254,8 @@
       </c>
       <c r="C5" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">리리</t>
+          <t xml:space="preserve">리
+리</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -3272,7 +3276,8 @@
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">도오</t>
+          <t xml:space="preserve">도
+오</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr">
@@ -3296,7 +3301,9 @@
       </c>
       <c r="C6" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">길리이</t>
+          <t xml:space="preserve">길
+리
+이</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -3342,7 +3349,8 @@
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">디리</t>
+          <t xml:space="preserve">디
+리</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -3697,7 +3705,8 @@
       </c>
       <c r="E16" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">니나</t>
+          <t xml:space="preserve">니
+나</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
@@ -3709,7 +3718,9 @@
       </c>
       <c r="G16" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">씨구나</t>
+          <t xml:space="preserve">씨
+구
+나</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -3740,7 +3751,8 @@
       </c>
       <c r="E17" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">노쇠</t>
+          <t xml:space="preserve">노
+쇠</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -3750,7 +3762,9 @@
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">좋구나</t>
+          <t xml:space="preserve">좋
+구
+나</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -3782,7 +3796,9 @@
       </c>
       <c r="E18" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">못하리</t>
+          <t xml:space="preserve">못
+하
+리</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
@@ -3795,7 +3811,9 @@
       </c>
       <c r="G18" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">지화자</t>
+          <t xml:space="preserve">지
+화
+자</t>
         </is>
       </c>
       <c r="H18" s="23" t="inlineStr">

--- a/sheets/민요/검수/창부타령 (채보1) 창부 타령-3.xlsx
+++ b/sheets/민요/검수/창부타령 (채보1) 창부 타령-3.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,24 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3155,7 +3178,7 @@
 姑</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">디
 리
@@ -3168,7 +3191,7 @@
 姑</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">애</t>
         </is>
@@ -3179,7 +3202,7 @@
 僙</t>
         </is>
       </c>
-      <c r="G3" s="24" t="inlineStr">
+      <c r="G3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">너</t>
         </is>
@@ -3190,7 +3213,7 @@
 僙</t>
         </is>
       </c>
-      <c r="I3" s="24" t="inlineStr">
+      <c r="I3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">핀</t>
         </is>
@@ -3203,7 +3226,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">리
 리</t>
@@ -3215,7 +3238,7 @@
 姑</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
@@ -3226,7 +3249,7 @@
 仲</t>
         </is>
       </c>
-      <c r="G4" s="25" t="inlineStr">
+      <c r="G4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
@@ -3237,7 +3260,7 @@
 仲</t>
         </is>
       </c>
-      <c r="I4" s="25" t="inlineStr">
+      <c r="I4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">득</t>
         </is>
@@ -3252,7 +3275,7 @@
 姑</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">리
 리</t>
@@ -3264,7 +3287,7 @@
 姑</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
@@ -3274,7 +3297,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">도
 오</t>
@@ -3285,7 +3308,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">슥</t>
         </is>
@@ -3299,7 +3322,7 @@
 潢</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">길
 리
@@ -3312,7 +3335,7 @@
 潢</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">진</t>
         </is>
@@ -3324,7 +3347,7 @@
 潢</t>
         </is>
       </c>
-      <c r="G6" s="26"/>
+      <c r="G6" s="32"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
@@ -3332,7 +3355,7 @@
 潢</t>
         </is>
       </c>
-      <c r="I6" s="26" t="inlineStr">
+      <c r="I6" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -3347,7 +3370,7 @@
 仲</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">디
 리</t>
@@ -3360,7 +3383,7 @@
 仲</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">못</t>
         </is>
@@ -3371,7 +3394,7 @@
 姑</t>
         </is>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="G7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -3381,7 +3404,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="I7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
@@ -3394,20 +3417,20 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="C8" s="27"/>
+      <c r="C8" s="33"/>
       <c r="D8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="E8" s="27"/>
+      <c r="E8" s="33"/>
       <c r="F8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙
 仲</t>
         </is>
       </c>
-      <c r="G8" s="27" t="inlineStr">
+      <c r="G8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">파</t>
         </is>
@@ -3418,7 +3441,7 @@
 仲</t>
         </is>
       </c>
-      <c r="I8" s="27" t="inlineStr">
+      <c r="I8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -3432,14 +3455,14 @@
 △</t>
         </is>
       </c>
-      <c r="C9" s="25"/>
+      <c r="C9" s="31"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -3449,7 +3472,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G9" s="25" t="inlineStr">
+      <c r="G9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
@@ -3459,7 +3482,7 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="I9" s="27"/>
+      <c r="I9" s="33"/>
     </row>
     <row r="10" ht="108.96" customHeight="1">
       <c r="A10" s="0"/>
@@ -3468,13 +3491,13 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="C10" s="28"/>
+      <c r="C10" s="34"/>
       <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="E10" s="28" t="inlineStr">
+      <c r="E10" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -3484,14 +3507,14 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="G10" s="28"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I10" s="26" t="inlineStr">
+      <c r="I10" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">슬</t>
         </is>
@@ -3505,14 +3528,14 @@
 潢</t>
         </is>
       </c>
-      <c r="C11" s="22"/>
+      <c r="C11" s="29"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -3523,7 +3546,7 @@
 △</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">못</t>
         </is>
@@ -3534,7 +3557,7 @@
 潢</t>
         </is>
       </c>
-      <c r="I11" s="24" t="inlineStr">
+      <c r="I11" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">플</t>
         </is>
@@ -3548,20 +3571,20 @@
 㳞</t>
         </is>
       </c>
-      <c r="C12" s="25"/>
+      <c r="C12" s="31"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E12" s="25"/>
+      <c r="E12" s="31"/>
       <c r="F12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙
 潢</t>
         </is>
       </c>
-      <c r="G12" s="27" t="inlineStr">
+      <c r="G12" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">살</t>
         </is>
@@ -3571,7 +3594,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I12" s="25" t="inlineStr">
+      <c r="I12" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
@@ -3584,20 +3607,20 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="C13" s="25"/>
+      <c r="C13" s="31"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E13" s="25"/>
+      <c r="E13" s="31"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="G13" s="25" t="inlineStr">
+      <c r="G13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">겟</t>
         </is>
@@ -3607,7 +3630,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I13" s="25"/>
+      <c r="I13" s="31"/>
     </row>
     <row r="14" ht="108.96" customHeight="1">
       <c r="A14" s="0"/>
@@ -3618,20 +3641,20 @@
 潢</t>
         </is>
       </c>
-      <c r="C14" s="26"/>
+      <c r="C14" s="32"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E14" s="26"/>
+      <c r="E14" s="32"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="G14" s="26" t="inlineStr">
+      <c r="G14" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
@@ -3642,7 +3665,7 @@
 無</t>
         </is>
       </c>
-      <c r="I14" s="26" t="inlineStr">
+      <c r="I14" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">쇠</t>
         </is>
@@ -3656,13 +3679,13 @@
 潢</t>
         </is>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="29"/>
       <c r="D15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -3672,7 +3695,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G15" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">열</t>
         </is>
@@ -3682,7 +3705,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="I15" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">숙</t>
         </is>
@@ -3695,7 +3718,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C16" s="25"/>
+      <c r="C16" s="31"/>
       <c r="D16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
@@ -3703,7 +3726,7 @@
 仲</t>
         </is>
       </c>
-      <c r="E16" s="27" t="inlineStr">
+      <c r="E16" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">니
 나</t>
@@ -3716,7 +3739,7 @@
 潢</t>
         </is>
       </c>
-      <c r="G16" s="27" t="inlineStr">
+      <c r="G16" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">씨
 구
@@ -3730,7 +3753,7 @@
 潢</t>
         </is>
       </c>
-      <c r="I16" s="25" t="inlineStr">
+      <c r="I16" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">명</t>
         </is>
@@ -3743,13 +3766,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C17" s="25"/>
+      <c r="C17" s="31"/>
       <c r="D17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="E17" s="27" t="inlineStr">
+      <c r="E17" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">노
 쇠</t>
@@ -3760,7 +3783,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G17" s="25" t="inlineStr">
+      <c r="G17" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">좋
 구
@@ -3772,7 +3795,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I17" s="25" t="inlineStr">
+      <c r="I17" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">적</t>
         </is>
@@ -3787,14 +3810,14 @@
 仲</t>
         </is>
       </c>
-      <c r="C18" s="26"/>
+      <c r="C18" s="32"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="E18" s="26" t="inlineStr">
+      <c r="E18" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">못
 하
@@ -3809,7 +3832,7 @@
 僙</t>
         </is>
       </c>
-      <c r="G18" s="28" t="inlineStr">
+      <c r="G18" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">지
 화
@@ -3824,7 +3847,7 @@
 僙</t>
         </is>
       </c>
-      <c r="I18" s="28" t="inlineStr">
+      <c r="I18" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">인</t>
         </is>

--- a/sheets/민요/검수/창부타령 (채보1) 창부 타령-3.xlsx
+++ b/sheets/민요/검수/창부타령 (채보1) 창부 타령-3.xlsx
@@ -402,7 +402,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄 16정간 양식("- 196 -")에 정간 번호 2개(1·2, 3·4 …)마다 가로선을 그어 큰 칸 8개로 씀, 칸마다 율명 2~3단 → 큰 칸 1개 = 정간 1개(위→아래 |), 8정간 4/4. 제목 "창부타령 3", 줄4 위에 "(2절끝)". 내용은 오른쪽 1~4줄, 5~8줄 빈 줄은 뺌. 가사는 각 율명 줄 오른쪽 칸(줄1 가사는 맨 오른쪽 칸). 古 모양은 姑, 兵 모양은 無로 적음. 줄3 정간6~8은 율명 없이 연음 표시만.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 16정간 양식("- 196 -")에 정간 번호 2개(1·2, 3·4 …)마다 가로선을 그어 큰 칸 8개로 씀, 칸마다 율명 2~3단 → 큰 칸 1개 = 정간 1개(위→아래 |), 8정간 4/4. 제목 "창부타령 3", 줄4 위에 "(2절끝)". 내용은 오른쪽 1~4줄, 5~8줄 빈 줄은 뺌. 가사는 각 율명 줄 오른쪽 칸(줄1 가사는 맨 오른쪽 칸). 古 모양은 姑, 兵 모양은 無로 적음. 줄3 정간6~8은 율명 없이 연음 표시만. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
@@ -1580,13 +1580,13 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無潢|汰|–</t>
+          <t xml:space="preserve">無潢|㴌|–</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
-汰
+㴌
 –</t>
         </is>
       </c>
@@ -1621,13 +1621,13 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|㳞汰|㳞㴌</t>
+          <t xml:space="preserve">–|㳞㴌|㳞㴌</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㳞汰
+㳞㴌
 㳞㴌</t>
         </is>
       </c>
@@ -1931,7 +1931,7 @@
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
-汰
+㴌
 –</t>
         </is>
       </c>
@@ -1990,7 +1990,7 @@
       <c r="B4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㳞汰
+㳞㴌
 㳞㴌</t>
         </is>
       </c>
